--- a/artfynd/A 23319-2025 artfynd.xlsx
+++ b/artfynd/A 23319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65464912</v>
+        <v>65464918</v>
       </c>
       <c r="B2" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608279.8711659753</v>
+        <v>608118</v>
       </c>
       <c r="R2" t="n">
-        <v>7018824.986913081</v>
+        <v>7018873</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>65464916</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608118.166801548</v>
+        <v>608118</v>
       </c>
       <c r="R3" t="n">
-        <v>7018873.13509211</v>
+        <v>7018873</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,50 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65464918</v>
+        <v>89616323</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Forsmo-Näsåker, Ång</t>
+          <t>Forsmo, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608118.166801548</v>
+        <v>608090</v>
       </c>
       <c r="R4" t="n">
-        <v>7018873.13509211</v>
+        <v>7018721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,18 +956,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Gammal björk</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gammal björk</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,12 +993,7 @@
         <v>65464903</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608091.1115740424</v>
+        <v>608091</v>
       </c>
       <c r="R5" t="n">
-        <v>7018806.027258597</v>
+        <v>7018806</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,19 +1058,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,53 +1087,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>65464914</v>
+        <v>126266288</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Forsmo-Näsåker, Ång</t>
+          <t>Bäcksvedjeberget, Bäcksvedjeberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608220.3608653297</v>
+        <v>608297</v>
       </c>
       <c r="R6" t="n">
-        <v>7018851.354436698</v>
+        <v>7018703</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,12 +1172,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1243,12 +1187,7 @@
         <v>89616310</v>
       </c>
       <c r="B7" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608289.2059549586</v>
+        <v>608289</v>
       </c>
       <c r="R7" t="n">
-        <v>7018788.824107058</v>
+        <v>7018789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,19 +1255,9 @@
           <t>2019-11-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-11-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,6 +1297,200 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>65464912</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Forsmo-Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608280</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7018825</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-07-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>65464914</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Forsmo-Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608220</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7018851</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-07-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-07-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23319-2025 artfynd.xlsx
+++ b/artfynd/A 23319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126266288</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89616310</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464918</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464916</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89616323</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464912</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464903</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,8 +1531,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464914</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>